--- a/travel/trips/2026-08-02_2026-08-09_mohonk-expense-report.xlsx
+++ b/travel/trips/2026-08-02_2026-08-09_mohonk-expense-report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peter\Documents\Group-2\travel\trips\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52D6A045-36A4-48A5-B4A6-25310027A614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1856E48E-89F4-4B19-AC94-2DE686EE1BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1749" windowWidth="10577" windowHeight="5365" xr2:uid="{5966F086-6AE1-4065-A4FD-346F3896E491}"/>
+    <workbookView xWindow="2263" yWindow="2263" windowWidth="15428" windowHeight="9454" xr2:uid="{A9DA3FAF-6937-458A-B34B-8010AEEEC99D}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="105">
   <si>
     <t>UNIFOCUS EXPENSE REPORT  |  Mohonk Mountain House</t>
   </si>
@@ -115,7 +115,7 @@
     <t>AA OMA-ORD-EWR (AA GFLPYC), ticket 0012349569454 - cash balance after flight credits, Visa -2674</t>
   </si>
   <si>
-    <t>Budget rental car, VW Atlas Cross Sport AWD, EWR pickup 8/2 2:45PM - return 8/7 5:00PM, agreement U266355924 (est. - confirm final charge/card at drop-off receipt)</t>
+    <t>Budget rental car, VW Atlas Cross Sport AWD, agreement 266355924, EWR pickup 8/2 2:45PM - actual return 8/7 3:37PM, 218 mi driven (odometer 3890-4108), Visa -2674, Net Charges confirmed USD 468.21, Total Due 0.00 - final receipt matches estimate exactly, no variance</t>
   </si>
   <si>
     <t>Car Rental</t>
@@ -178,6 +178,12 @@
     <t>McDonald's #26777 (ORD Terminal 3) - breakfast, layover on return home, Visa -2674</t>
   </si>
   <si>
+    <t>Omaha Eppley Airfield (OMA) short-term parking, entry 8/2 05:41 - exit 8/3 07:46, receipt 13366 - paid by Brian Brazeal (Capital One Visa -9323) who borrowed Pete's car from OMA for the week; Pete to reimburse Brian, claimed on ER</t>
+  </si>
+  <si>
+    <t>Parking</t>
+  </si>
+  <si>
     <t>TOTAL</t>
   </si>
   <si>
@@ -235,7 +241,7 @@
     <t>-2674</t>
   </si>
   <si>
-    <t>Visa SW Rapid Rewards+ (flight cash balance, return flight, Taco Bell, gas, hotel + fees, both Ubers, Scarpetta, Chick Chick, E-ZPass, ORD breakfast)</t>
+    <t>Visa SW Rapid Rewards+ (flight cash balance, return flight, Taco Bell, gas, hotel + fees, both Ubers, Scarpetta, Chick Chick, E-ZPass, ORD breakfast, Budget rental car)</t>
   </si>
   <si>
     <t>SW Credit</t>
@@ -256,10 +262,10 @@
     <t>Visa WF Active Cash (Tallow - Shaver Hall dinner, full billable value; net card charge was .77 after credit)</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>Budget rental car - confirm card used at drop-off</t>
+    <t>-9323</t>
+  </si>
+  <si>
+    <t>Capital One Visa (Brian Brazeal) - OMA short-term parking, Pete to reimburse Brian</t>
   </si>
   <si>
     <t>OPEN ITEMS BEFORE SUBMISSION</t>
@@ -520,10 +526,10 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -883,11 +889,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C638474-0CB8-463C-A475-97FADC8D2292}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E1230F-6C72-4073-ACBA-406F7FF36C7C}">
   <sheetPr>
     <tabColor rgb="FF64381F"/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.69140625" customWidth="1"/>
@@ -898,7 +904,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -907,7 +913,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>4</v>
@@ -918,10 +924,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C3" s="28"/>
       <c r="D3" s="28"/>
@@ -929,10 +935,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
@@ -940,7 +946,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B5" s="28" t="s">
         <v>18</v>
@@ -951,10 +957,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C6" s="28"/>
       <c r="D6" s="28"/>
@@ -962,10 +968,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C7" s="28"/>
       <c r="D7" s="28"/>
@@ -973,7 +979,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" s="29" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -988,7 +994,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
@@ -1081,54 +1087,54 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A19" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="10">
+        <v>34.5</v>
+      </c>
+      <c r="C19" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A20" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B20" s="32">
         <v>4.96</v>
       </c>
-      <c r="C19" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A20" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="26">
-        <f>SUM(B11:B19)</f>
-        <v>2429.06</v>
-      </c>
-      <c r="C20" s="24"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A22" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
+      <c r="C20" s="33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A21" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="26">
+        <f>SUM(B11:B20)</f>
+        <v>2463.56</v>
+      </c>
+      <c r="C21" s="24"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A23" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="B23" s="30" t="s">
+      <c r="A23" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A24" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="30" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A24" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="32">
-        <v>1595.58</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.4">
@@ -1139,7 +1145,7 @@
         <v>66</v>
       </c>
       <c r="C25" s="10">
-        <v>311.8</v>
+        <v>2063.79</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.4">
@@ -1150,7 +1156,7 @@
         <v>68</v>
       </c>
       <c r="C26" s="32">
-        <v>19.850000000000001</v>
+        <v>311.8</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.4">
@@ -1161,7 +1167,7 @@
         <v>70</v>
       </c>
       <c r="C27" s="10">
-        <v>33.619999999999997</v>
+        <v>19.850000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.4">
@@ -1172,40 +1178,42 @@
         <v>72</v>
       </c>
       <c r="C28" s="32">
-        <v>468.21</v>
+        <v>33.619999999999997</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A29" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="26">
-        <f>SUM(C24:C28)</f>
-        <v>2429.0599999999995</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A31" s="35" t="s">
+      <c r="A29" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
+      <c r="B29" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="10">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A30" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="24"/>
+      <c r="C30" s="26">
+        <f>SUM(C25:C29)</f>
+        <v>2463.56</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A32" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
+      <c r="A32" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1214,22 +1222,31 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A35:E35"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A23:E23"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:E34"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B3:E3"/>
@@ -1242,11 +1259,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FABE12CC-00D8-4186-B6A2-AA99B57CE0A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EFD3B56-7E85-4195-9970-2C10B5C777BD}">
   <sheetPr>
     <tabColor rgb="FFB6752E"/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.69140625" customWidth="1"/>
@@ -1940,24 +1957,38 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A23" s="8"/>
+      <c r="A23" s="8">
+        <v>46236</v>
+      </c>
       <c r="B23" s="9" t="str">
-        <f>IF(A23="","",TEXT(A23,"ddd"))</f>
-        <v/>
-      </c>
-      <c r="C23" s="20"/>
+        <f>TEXT(A23,"ddd")</f>
+        <v>Sun</v>
+      </c>
+      <c r="C23" s="10">
+        <v>34.5</v>
+      </c>
       <c r="D23" s="11">
         <v>1</v>
       </c>
       <c r="E23" s="10">
         <f>C23*D23</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="21"/>
+        <v>34.5</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="14"/>
@@ -1965,7 +1996,7 @@
         <f>IF(A24="","",TEXT(A24,"ddd"))</f>
         <v/>
       </c>
-      <c r="C24" s="22"/>
+      <c r="C24" s="20"/>
       <c r="D24" s="17">
         <v>1</v>
       </c>
@@ -1977,7 +2008,7 @@
       <c r="G24" s="18"/>
       <c r="H24" s="18"/>
       <c r="I24" s="18"/>
-      <c r="J24" s="23"/>
+      <c r="J24" s="21"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" s="8"/>
@@ -1985,7 +2016,7 @@
         <f>IF(A25="","",TEXT(A25,"ddd"))</f>
         <v/>
       </c>
-      <c r="C25" s="20"/>
+      <c r="C25" s="22"/>
       <c r="D25" s="11">
         <v>1</v>
       </c>
@@ -1997,7 +2028,7 @@
       <c r="G25" s="12"/>
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
-      <c r="J25" s="21"/>
+      <c r="J25" s="23"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" s="14"/>
@@ -2005,7 +2036,7 @@
         <f>IF(A26="","",TEXT(A26,"ddd"))</f>
         <v/>
       </c>
-      <c r="C26" s="22"/>
+      <c r="C26" s="20"/>
       <c r="D26" s="17">
         <v>1</v>
       </c>
@@ -2017,7 +2048,7 @@
       <c r="G26" s="18"/>
       <c r="H26" s="18"/>
       <c r="I26" s="18"/>
-      <c r="J26" s="23"/>
+      <c r="J26" s="21"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" s="8"/>
@@ -2025,7 +2056,7 @@
         <f>IF(A27="","",TEXT(A27,"ddd"))</f>
         <v/>
       </c>
-      <c r="C27" s="20"/>
+      <c r="C27" s="22"/>
       <c r="D27" s="11">
         <v>1</v>
       </c>
@@ -2037,7 +2068,7 @@
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
-      <c r="J27" s="21"/>
+      <c r="J27" s="23"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" s="14"/>
@@ -2045,7 +2076,7 @@
         <f>IF(A28="","",TEXT(A28,"ddd"))</f>
         <v/>
       </c>
-      <c r="C28" s="22"/>
+      <c r="C28" s="20"/>
       <c r="D28" s="17">
         <v>1</v>
       </c>
@@ -2057,7 +2088,7 @@
       <c r="G28" s="18"/>
       <c r="H28" s="18"/>
       <c r="I28" s="18"/>
-      <c r="J28" s="23"/>
+      <c r="J28" s="21"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="8"/>
@@ -2065,7 +2096,7 @@
         <f>IF(A29="","",TEXT(A29,"ddd"))</f>
         <v/>
       </c>
-      <c r="C29" s="20"/>
+      <c r="C29" s="22"/>
       <c r="D29" s="11">
         <v>1</v>
       </c>
@@ -2077,7 +2108,7 @@
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
-      <c r="J29" s="21"/>
+      <c r="J29" s="23"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" s="14"/>
@@ -2085,7 +2116,7 @@
         <f>IF(A30="","",TEXT(A30,"ddd"))</f>
         <v/>
       </c>
-      <c r="C30" s="22"/>
+      <c r="C30" s="20"/>
       <c r="D30" s="17">
         <v>1</v>
       </c>
@@ -2097,7 +2128,7 @@
       <c r="G30" s="18"/>
       <c r="H30" s="18"/>
       <c r="I30" s="18"/>
-      <c r="J30" s="23"/>
+      <c r="J30" s="21"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A31" s="8"/>
@@ -2105,7 +2136,7 @@
         <f>IF(A31="","",TEXT(A31,"ddd"))</f>
         <v/>
       </c>
-      <c r="C31" s="20"/>
+      <c r="C31" s="22"/>
       <c r="D31" s="11">
         <v>1</v>
       </c>
@@ -2117,7 +2148,7 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
-      <c r="J31" s="21"/>
+      <c r="J31" s="23"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A32" s="14"/>
@@ -2125,7 +2156,7 @@
         <f>IF(A32="","",TEXT(A32,"ddd"))</f>
         <v/>
       </c>
-      <c r="C32" s="22"/>
+      <c r="C32" s="20"/>
       <c r="D32" s="17">
         <v>1</v>
       </c>
@@ -2137,34 +2168,54 @@
       <c r="G32" s="18"/>
       <c r="H32" s="18"/>
       <c r="I32" s="18"/>
-      <c r="J32" s="23"/>
+      <c r="J32" s="21"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A33" s="24"/>
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="E33" s="26">
-        <f>SUM(E5:E32)</f>
-        <v>2429.06</v>
-      </c>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="24"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="9" t="str">
+        <f>IF(A33="","",TEXT(A33,"ddd"))</f>
+        <v/>
+      </c>
+      <c r="C33" s="22"/>
+      <c r="D33" s="11">
+        <v>1</v>
+      </c>
+      <c r="E33" s="10">
+        <f>C33*D33</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="23"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A34" s="24"/>
+      <c r="B34" s="24"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="E34" s="26">
+        <f>SUM(E5:E33)</f>
+        <v>2463.56</v>
+      </c>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F32" xr:uid="{C6ECC75D-C667-48BE-8075-0549477EADB0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F33" xr:uid="{E6D9AE04-0F43-46AA-863D-F00E64B85D66}">
       <formula1>"UF,PERSONAL,OTHER"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H32" xr:uid="{356F0088-ABF6-48BD-8B50-E14A627CFCF8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H33" xr:uid="{B0661D6E-323E-45D4-981F-EA9E6E27243F}">
       <formula1>"Air Fare,Taxi/Train/Bus,Car Rental,Gas/Tolls,Parking,Hotel,Bkfst,Lunch,Dinner,Phone/Data,Computer,Other,Postage,Misc"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2173,7 +2224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD867586-0F30-4DEB-BB51-E9E5E6E9A6AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2318F84D-DF98-4C5B-B25F-41AB49DE6C53}">
   <sheetPr>
     <tabColor rgb="FFF0E4D6"/>
   </sheetPr>
@@ -2185,132 +2236,132 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/travel/trips/2026-08-02_2026-08-09_mohonk-expense-report.xlsx
+++ b/travel/trips/2026-08-02_2026-08-09_mohonk-expense-report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peter\Documents\Group-2\travel\trips\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1856E48E-89F4-4B19-AC94-2DE686EE1BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F51C584-A73E-42D0-8761-0D9095DCD0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2263" yWindow="2263" windowWidth="15428" windowHeight="9454" xr2:uid="{A9DA3FAF-6937-458A-B34B-8010AEEEC99D}"/>
+    <workbookView xWindow="2263" yWindow="2263" windowWidth="15428" windowHeight="9454" xr2:uid="{6A06982B-AC92-48BF-8175-DAEB804979ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="115">
   <si>
     <t>UNIFOCUS EXPENSE REPORT  |  Mohonk Mountain House</t>
   </si>
@@ -88,100 +88,118 @@
     <t>Charge Code</t>
   </si>
   <si>
+    <t>Charge Source</t>
+  </si>
+  <si>
     <t>PERSONAL</t>
   </si>
   <si>
-    <t>McDonald's mobile order, 568 Myrtle Ave, Boonton NJ - Bacon Quarter Pounder w/Cheese Large Meal (fries, unsweetened iced tea), Visa -8289</t>
+    <t>SW OMA-ORD-EWR (AA GFLPYC), ticket 0012349569454 (outbound leg of round trip)</t>
+  </si>
+  <si>
+    <t>Air Fare</t>
+  </si>
+  <si>
+    <t>Mohonk Mountain House</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>AA Flight Credit [AA-2026-001] (source: Visa -2674, per flight-credits.md)</t>
+  </si>
+  <si>
+    <t>AA Flight Credit [AA-2026-002] (source: Visa -2674, per flight-credits.md)</t>
+  </si>
+  <si>
+    <t>AA OMA-ORD-EWR (AA GFLPYC), ticket 0012349569454 - cash balance after flight credits (outbound leg of round trip)</t>
+  </si>
+  <si>
+    <t>Visa -2674</t>
+  </si>
+  <si>
+    <t>AA EWR-ORD-OMA (AA JMTNHX), ticket 0012362823941 - return leg, dated with outbound per round-trip convention; cancelled 8/7 for weather, rebooked by AA to 8/9 at no additional charge</t>
+  </si>
+  <si>
+    <t>Budget rental car, VW Atlas Cross Sport AWD, agreement 266355924, EWR pickup 8/2 2:45PM - actual return 8/7 3:37PM, 218 mi driven (odometer 3890-4108), Net Charges confirmed USD 468.21, Total Due 0.00 - final receipt matches estimate exactly, no variance</t>
+  </si>
+  <si>
+    <t>Car Rental</t>
+  </si>
+  <si>
+    <t>McDonald's mobile order, 568 Myrtle Ave, Boonton NJ (3:30 PM) - Bacon Quarter Pounder w/Cheese Large Meal (fries, unsweetened iced tea)</t>
   </si>
   <si>
     <t>Lunch</t>
   </si>
   <si>
-    <t>Mohonk Mountain House</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>SW OMA-ORD-EWR (AA GFLPYC), ticket 0012349569454 - Flight Credit [AA-2026-001]</t>
-  </si>
-  <si>
-    <t>Air Fare</t>
-  </si>
-  <si>
-    <t>SW OMA-ORD-EWR (AA GFLPYC), ticket 0012349569454 - Flight Credit [AA-2026-002]</t>
-  </si>
-  <si>
-    <t>AA OMA-ORD-EWR (AA GFLPYC), ticket 0012349569454 - cash balance after flight credits, Visa -2674</t>
-  </si>
-  <si>
-    <t>Budget rental car, VW Atlas Cross Sport AWD, agreement 266355924, EWR pickup 8/2 2:45PM - actual return 8/7 3:37PM, 218 mi driven (odometer 3890-4108), Visa -2674, Net Charges confirmed USD 468.21, Total Due 0.00 - final receipt matches estimate exactly, no variance</t>
-  </si>
-  <si>
-    <t>Car Rental</t>
-  </si>
-  <si>
-    <t>Taco Bell #040713, 238 Main St, New Paltz NY (senior discount applied), Visa -2674</t>
-  </si>
-  <si>
-    <t>QuickChek #146, Whippany NJ - gas, rental car, 7.396 gal @ .959/gal, Visa -2674</t>
+    <t>Visa -8289</t>
+  </si>
+  <si>
+    <t>E-ZPass NY toll near New Paltz, NY (outbound, EWR to Mohonk, later in the drive) - Temporary Travel Account ending xxxxxx8500, paid 8/8/26, confirmed by phone with E-ZPass NY as the only toll registered on the rental (no return-leg toll)</t>
   </si>
   <si>
     <t>Gas/Tolls</t>
   </si>
   <si>
-    <t>AA EWR-ORD-OMA (AA JMTNHX), ticket 0012362823941 - cancelled 8/7 for weather, rebooked by AA to 8/9 at no additional charge, Visa -2674</t>
-  </si>
-  <si>
-    <t>Hotel Seville Nomad (weather-delay hotel, EWR cancellation), 2 nights, Hyatt folio 2529375976, Hotels.com itinerary 73517117133488, Visa -2674</t>
+    <t>Omaha Eppley Airfield (OMA) short-term parking, entry 8/2 05:41 - exit 8/3 07:46, receipt 13366 - paid by Brian Brazeal who borrowed Pete's car from OMA for the week; Pete to reimburse Brian, claimed on ER</t>
+  </si>
+  <si>
+    <t>Parking</t>
+  </si>
+  <si>
+    <t>Capital One Visa -9323 (Brian Brazeal)</t>
+  </si>
+  <si>
+    <t>Taco Bell #040713, 238 Main St, New Paltz NY (senior discount applied) - lunch, on way down from Mohonk</t>
+  </si>
+  <si>
+    <t>QuickChek #146, Whippany NJ - gas, rental car, before drop-off, 7.396 gal @ .959/gal</t>
+  </si>
+  <si>
+    <t>Hotel Seville Nomad (weather-delay hotel, booked after EWR cancellation), 2 nights, Hyatt folio 2529375976, Hotels.com itinerary 73517117133488</t>
   </si>
   <si>
     <t>Hotel</t>
   </si>
   <si>
-    <t>Uber, EWR Terminal A to Hotel Seville Nomad (weather-delay), UberXL, driver Oleg, 17.82 mi/54 min, Visa -2674</t>
+    <t>Uber, EWR Terminal A (8:09 PM) to Hotel Seville Nomad (9:03 PM), UberXL, driver Oleg, 17.82 mi/54 min</t>
   </si>
   <si>
     <t>Taxi/Train/Bus</t>
   </si>
   <si>
-    <t>Scarpetta/LDV Hospitality (88 Madison Ave, NYC) - dinner during weather delay, Restaurant Week prix fixe, Visa -2674</t>
+    <t>Scarpetta/LDV Hospitality (88 Madison Ave, NYC) - dinner after arriving hotel, Restaurant Week prix fixe</t>
   </si>
   <si>
     <t>Dinner</t>
   </si>
   <si>
-    <t>McDonald's mobile order (401 Park Ave S, NYC) - breakfast during weather delay, Egg McMuffin + large unsweetened iced tea, Visa -8289</t>
+    <t>McDonald's mobile order (401 Park Ave S, NYC) - breakfast, Egg McMuffin + large unsweetened iced tea</t>
   </si>
   <si>
     <t>Bkfst</t>
   </si>
   <si>
-    <t>Tallow - Shaver Hall (424 5th Ave, NYC) - dinner take-out during weather delay, full billable meal value (.85 food + .77 tip); -.85 credit applied, net card charge .77, Visa -7552 (WF Active Cash)</t>
-  </si>
-  <si>
-    <t>Chick Chick at Shaver Hall (424 5th Ave, NYC) - drink after Tallow dinner, Visa -2674</t>
+    <t>Tallow - Shaver Hall (424 5th Ave, NYC) - dinner take-out, full billable meal value (.85 food + .77 tip); -.85 credit applied, net card charge .77</t>
+  </si>
+  <si>
+    <t>Visa -7552 (WF Active Cash)</t>
+  </si>
+  <si>
+    <t>Chick Chick at Shaver Hall (424 5th Ave, NYC) - drink after Tallow dinner</t>
   </si>
   <si>
     <t>Other</t>
   </si>
   <si>
-    <t>E-ZPass NY toll near New Paltz, NY (outbound, EWR to Mohonk) - Temporary Travel Account ending xxxxxx8500, paid 8/8/26, confirmed by phone with E-ZPass NY as the only toll registered on the rental (no return-leg toll), Visa -2674</t>
-  </si>
-  <si>
-    <t>Hotel Seville Nomad - mandatory fees due at property (Destination Fee /night x2 + NYC taxes), Hyatt folio 2529375976, Visa -2674</t>
-  </si>
-  <si>
-    <t>Uber, Hotel Seville Nomad to EWR Terminal A (weather-delay return), UberX, driver Muhammad, 19.45 mi/31 min, Visa -2674</t>
-  </si>
-  <si>
-    <t>McDonald's #26777 (ORD Terminal 3) - breakfast, layover on return home, Visa -2674</t>
-  </si>
-  <si>
-    <t>Omaha Eppley Airfield (OMA) short-term parking, entry 8/2 05:41 - exit 8/3 07:46, receipt 13366 - paid by Brian Brazeal (Capital One Visa -9323) who borrowed Pete's car from OMA for the week; Pete to reimburse Brian, claimed on ER</t>
-  </si>
-  <si>
-    <t>Parking</t>
+    <t>Uber, Hotel Seville Nomad (3:01 AM) to EWR Terminal A (3:33 AM), UberX, driver Muhammad, 19.45 mi/31 min</t>
+  </si>
+  <si>
+    <t>Hotel Seville Nomad - mandatory fees, folio checkout ~4:17 AM (after physical departure via Uber) (Destination Fee /night x2 + NYC taxes), Hyatt folio 2529375976</t>
+  </si>
+  <si>
+    <t>McDonald's #26777 (ORD Terminal 3, 6:56 AM) - breakfast, layover on return home</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -218,6 +236,18 @@
   </si>
   <si>
     <t>Hotel at Mohonk itself comped by property (Room 165, confirmation 7833637490-1) - not included in reimbursement total. Return flight cancelled 8/7 for weather; AA rebooked to 8/9 at no additional fare. All weather-delay expenses (hotel, Uber, meals 8/7-8/9) are billable on this ER per trip receipt log.</t>
+  </si>
+  <si>
+    <t>Weather Delay Justification</t>
+  </si>
+  <si>
+    <t>Original return AA JMTNHX (EWR-ORD-OMA) cancelled by American Airlines 8/7/26 due to weather - no flight operations resumed until 8/9. AA rebooked at no additional fare: EWR dep 5:29 AM (AA2917) - ORD arr 7:15 AM - ORD dep 8:03 AM (AA6389, SkyWest/American Eagle) - OMA arr 9:49 AM. AA rebooking confirmation to be attached as supporting documentation.</t>
+  </si>
+  <si>
+    <t>Notification</t>
+  </si>
+  <si>
+    <t>Both Unifocus and Mohonk Mountain House were notified of the weather delay by Pete. Both acknowledged and are not concerned about the resulting added expense.</t>
   </si>
   <si>
     <t>SUMMARY BY CATEGORY</t>
@@ -483,7 +513,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -496,6 +526,9 @@
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -889,11 +922,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E1230F-6C72-4073-ACBA-406F7FF36C7C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{304F2538-6469-4F3D-933C-8B1D9CACBFBB}">
   <sheetPr>
     <tabColor rgb="FF64381F"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.69140625" customWidth="1"/>
@@ -903,8 +936,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="27" t="s">
-        <v>48</v>
+      <c r="A1" s="28" t="s">
+        <v>54</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -913,339 +946,363 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
+        <v>56</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
+        <v>58</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
+        <v>60</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
+        <v>61</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
+        <v>63</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A9" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A10" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>60</v>
-      </c>
+      <c r="A9" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A11" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="10">
-        <v>905.4</v>
-      </c>
-      <c r="C11" s="9">
-        <v>4</v>
-      </c>
+      <c r="A11" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="32">
+        <v>12</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A13" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="11">
+        <v>905.4</v>
+      </c>
+      <c r="C13" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A14" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="33">
         <v>468.21</v>
       </c>
-      <c r="C12" s="33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A13" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="10">
+      <c r="C14" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A15" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="11">
         <v>615.26</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C15" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A14" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="32">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A16" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="33">
         <v>242.79</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C16" s="34">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A15" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="10">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A17" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="11">
         <v>110.94</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C17" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A16" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="32">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A18" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="33">
         <v>24.88</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C18" s="34">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A17" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="10">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A19" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="11">
         <v>23.6</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C19" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A18" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="32">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A20" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="33">
         <v>33.020000000000003</v>
       </c>
-      <c r="C18" s="33">
+      <c r="C20" s="34">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A19" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="10">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A21" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="11">
         <v>34.5</v>
       </c>
-      <c r="C19" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A20" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="32">
+      <c r="C21" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A22" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="33">
         <v>4.96</v>
       </c>
-      <c r="C20" s="33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A21" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21" s="26">
-        <f>SUM(B11:B20)</f>
+      <c r="C22" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A23" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="27">
+        <f>SUM(B13:B22)</f>
         <v>2463.56</v>
       </c>
-      <c r="C21" s="24"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A23" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A24" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="30" t="s">
+      <c r="C23" s="25"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A25" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A26" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="31" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A25" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="10">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A27" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="11">
         <v>2063.79</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A26" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="32">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A28" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="33">
         <v>311.8</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A27" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" s="10">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A29" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" s="11">
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A28" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" s="32">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A30" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="33">
         <v>33.619999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A29" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="10">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A31" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="11">
         <v>34.5</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A30" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="B30" s="24"/>
-      <c r="C30" s="26">
-        <f>SUM(C25:C29)</f>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A32" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="25"/>
+      <c r="C32" s="27">
+        <f>SUM(C27:C31)</f>
         <v>2463.56</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A32" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A33" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-    </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A34" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
+      <c r="A34" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
     </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
     <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A37:E37"/>
     <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B2:E2"/>
@@ -1259,11 +1316,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EFD3B56-7E85-4195-9970-2C10B5C777BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA6B548-1C31-4F3A-87A5-7F6E227AC84F}">
   <sheetPr>
     <tabColor rgb="FFB6752E"/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.69140625" customWidth="1"/>
@@ -1272,13 +1329,15 @@
     <col min="4" max="4" width="9.69140625" customWidth="1"/>
     <col min="5" max="5" width="11.69140625" customWidth="1"/>
     <col min="6" max="6" width="10.69140625" customWidth="1"/>
-    <col min="7" max="7" width="48.69140625" customWidth="1"/>
+    <col min="7" max="7" width="44.69140625" customWidth="1"/>
     <col min="8" max="8" width="12.69140625" customWidth="1"/>
     <col min="9" max="9" width="22.69140625" customWidth="1"/>
     <col min="10" max="10" width="10.69140625" customWidth="1"/>
+    <col min="11" max="11" width="3.69140625" customWidth="1"/>
+    <col min="12" max="12" width="20.69140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1291,8 +1350,10 @@
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1312,7 +1373,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
@@ -1343,879 +1404,981 @@
       <c r="J4" s="7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A5" s="8">
+      <c r="K4" s="8"/>
+      <c r="L4" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A5" s="9">
         <v>46236</v>
       </c>
-      <c r="B5" s="9" t="str">
+      <c r="B5" s="10" t="str">
         <f>TEXT(A5,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C5" s="10">
-        <v>12.25</v>
-      </c>
-      <c r="D5" s="11">
-        <v>1</v>
-      </c>
-      <c r="E5" s="10">
+      <c r="C5" s="11">
+        <v>272.10000000000002</v>
+      </c>
+      <c r="D5" s="12">
+        <v>1</v>
+      </c>
+      <c r="E5" s="11">
         <f>C5*D5</f>
-        <v>12.25</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="12" t="s">
+        <v>272.10000000000002</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="G5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="H5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="I5" s="13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A6" s="14">
+      <c r="J5" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A6" s="15">
         <v>46236</v>
       </c>
-      <c r="B6" s="15" t="str">
+      <c r="B6" s="16" t="str">
         <f>TEXT(A6,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C6" s="16">
-        <v>272.10000000000002</v>
-      </c>
-      <c r="D6" s="17">
-        <v>1</v>
-      </c>
-      <c r="E6" s="16">
+      <c r="C6" s="17">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="D6" s="18">
+        <v>1</v>
+      </c>
+      <c r="E6" s="17">
         <f>C6*D6</f>
-        <v>272.10000000000002</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="18" t="s">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A7" s="8">
+      <c r="K6" s="13"/>
+      <c r="L6" s="19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A7" s="9">
         <v>46236</v>
       </c>
-      <c r="B7" s="9" t="str">
+      <c r="B7" s="10" t="str">
         <f>TEXT(A7,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C7" s="10">
-        <v>39.700000000000003</v>
-      </c>
-      <c r="D7" s="11">
-        <v>1</v>
-      </c>
-      <c r="E7" s="10">
+      <c r="C7" s="11">
+        <v>146.4</v>
+      </c>
+      <c r="D7" s="12">
+        <v>1</v>
+      </c>
+      <c r="E7" s="11">
         <f>C7*D7</f>
-        <v>39.700000000000003</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="12" t="s">
+        <v>146.4</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="I7" s="13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A8" s="14">
+      <c r="J7" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A8" s="15">
         <v>46236</v>
       </c>
-      <c r="B8" s="15" t="str">
+      <c r="B8" s="16" t="str">
         <f>TEXT(A8,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C8" s="16">
-        <v>146.4</v>
-      </c>
-      <c r="D8" s="17">
-        <v>1</v>
-      </c>
-      <c r="E8" s="16">
+      <c r="C8" s="17">
+        <v>447.2</v>
+      </c>
+      <c r="D8" s="18">
+        <v>1</v>
+      </c>
+      <c r="E8" s="17">
         <f>C8*D8</f>
-        <v>146.4</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="18" t="s">
+        <v>447.2</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="J8" s="19" t="s">
+      <c r="I8" s="19" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A9" s="8">
+      <c r="J8" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="13"/>
+      <c r="L8" s="19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A9" s="9">
         <v>46236</v>
       </c>
-      <c r="B9" s="9" t="str">
+      <c r="B9" s="10" t="str">
         <f>TEXT(A9,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="11">
         <v>468.21</v>
       </c>
-      <c r="D9" s="11">
-        <v>1</v>
-      </c>
-      <c r="E9" s="10">
+      <c r="D9" s="12">
+        <v>1</v>
+      </c>
+      <c r="E9" s="11">
         <f>C9*D9</f>
         <v>468.21</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="12" t="s">
+      <c r="F9" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="13" t="s">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A10" s="15">
+        <v>46236</v>
+      </c>
+      <c r="B10" s="16" t="str">
+        <f>TEXT(A10,"ddd")</f>
+        <v>Sun</v>
+      </c>
+      <c r="C10" s="17">
+        <v>12.25</v>
+      </c>
+      <c r="D10" s="18">
+        <v>1</v>
+      </c>
+      <c r="E10" s="17">
+        <f>C10*D10</f>
+        <v>12.25</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="19" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A10" s="14">
+      <c r="J10" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="13"/>
+      <c r="L10" s="19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A11" s="9">
+        <v>46236</v>
+      </c>
+      <c r="B11" s="10" t="str">
+        <f>TEXT(A11,"ddd")</f>
+        <v>Sun</v>
+      </c>
+      <c r="C11" s="11">
+        <v>3.74</v>
+      </c>
+      <c r="D11" s="12">
+        <v>1</v>
+      </c>
+      <c r="E11" s="11">
+        <f>C11*D11</f>
+        <v>3.74</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A12" s="15">
+        <v>46237</v>
+      </c>
+      <c r="B12" s="16" t="str">
+        <f>TEXT(A12,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C12" s="17">
+        <v>34.5</v>
+      </c>
+      <c r="D12" s="18">
+        <v>1</v>
+      </c>
+      <c r="E12" s="17">
+        <f>C12*D12</f>
+        <v>34.5</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="13"/>
+      <c r="L12" s="19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A13" s="9">
         <v>46241</v>
       </c>
-      <c r="B10" s="15" t="str">
-        <f>TEXT(A10,"ddd")</f>
-        <v>Fri</v>
-      </c>
-      <c r="C10" s="16">
-        <v>12.63</v>
-      </c>
-      <c r="D10" s="17">
-        <v>1</v>
-      </c>
-      <c r="E10" s="16">
-        <f>C10*D10</f>
-        <v>12.63</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A11" s="8">
-        <v>46241</v>
-      </c>
-      <c r="B11" s="9" t="str">
-        <f>TEXT(A11,"ddd")</f>
-        <v>Fri</v>
-      </c>
-      <c r="C11" s="10">
-        <v>29.28</v>
-      </c>
-      <c r="D11" s="11">
-        <v>1</v>
-      </c>
-      <c r="E11" s="10">
-        <f>C11*D11</f>
-        <v>29.28</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A12" s="14">
-        <v>46241</v>
-      </c>
-      <c r="B12" s="15" t="str">
-        <f>TEXT(A12,"ddd")</f>
-        <v>Fri</v>
-      </c>
-      <c r="C12" s="16">
-        <v>447.2</v>
-      </c>
-      <c r="D12" s="17">
-        <v>1</v>
-      </c>
-      <c r="E12" s="16">
-        <f>C12*D12</f>
-        <v>447.2</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A13" s="8">
-        <v>46241</v>
-      </c>
-      <c r="B13" s="9" t="str">
+      <c r="B13" s="10" t="str">
         <f>TEXT(A13,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C13" s="10">
-        <v>512</v>
-      </c>
-      <c r="D13" s="11">
-        <v>1</v>
-      </c>
-      <c r="E13" s="10">
+      <c r="C13" s="11">
+        <v>12.63</v>
+      </c>
+      <c r="D13" s="12">
+        <v>1</v>
+      </c>
+      <c r="E13" s="11">
         <f>C13*D13</f>
-        <v>512</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="13" t="s">
+        <v>12.63</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A14" s="14">
+      <c r="J13" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A14" s="15">
         <v>46241</v>
       </c>
-      <c r="B14" s="15" t="str">
+      <c r="B14" s="16" t="str">
         <f>TEXT(A14,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C14" s="16">
-        <v>129.13999999999999</v>
-      </c>
-      <c r="D14" s="17">
-        <v>1</v>
-      </c>
-      <c r="E14" s="16">
+      <c r="C14" s="17">
+        <v>29.28</v>
+      </c>
+      <c r="D14" s="18">
+        <v>1</v>
+      </c>
+      <c r="E14" s="17">
         <f>C14*D14</f>
-        <v>129.13999999999999</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="18" t="s">
+        <v>29.28</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="19" t="s">
+      <c r="I14" s="19" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A15" s="8">
+      <c r="J14" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" s="13"/>
+      <c r="L14" s="19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A15" s="9">
         <v>46241</v>
       </c>
-      <c r="B15" s="9" t="str">
+      <c r="B15" s="10" t="str">
         <f>TEXT(A15,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="11">
+        <v>512</v>
+      </c>
+      <c r="D15" s="12">
+        <v>1</v>
+      </c>
+      <c r="E15" s="11">
+        <f>C15*D15</f>
+        <v>512</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A16" s="15">
+        <v>46241</v>
+      </c>
+      <c r="B16" s="16" t="str">
+        <f>TEXT(A16,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C16" s="17">
+        <v>129.13999999999999</v>
+      </c>
+      <c r="D16" s="18">
+        <v>1</v>
+      </c>
+      <c r="E16" s="17">
+        <f>C16*D16</f>
+        <v>129.13999999999999</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" s="13"/>
+      <c r="L16" s="19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A17" s="9">
+        <v>46241</v>
+      </c>
+      <c r="B17" s="10" t="str">
+        <f>TEXT(A17,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C17" s="11">
         <v>77.319999999999993</v>
       </c>
-      <c r="D15" s="11">
-        <v>1</v>
-      </c>
-      <c r="E15" s="10">
-        <f>C15*D15</f>
+      <c r="D17" s="12">
+        <v>1</v>
+      </c>
+      <c r="E17" s="11">
+        <f>C17*D17</f>
         <v>77.319999999999993</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" s="13" t="s">
+      <c r="F17" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="I17" s="13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A16" s="14">
+      <c r="J17" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A18" s="15">
         <v>46242</v>
       </c>
-      <c r="B16" s="15" t="str">
-        <f>TEXT(A16,"ddd")</f>
-        <v>Sat</v>
-      </c>
-      <c r="C16" s="16">
-        <v>7.6</v>
-      </c>
-      <c r="D16" s="17">
-        <v>1</v>
-      </c>
-      <c r="E16" s="16">
-        <f>C16*D16</f>
-        <v>7.6</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="I16" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A17" s="8">
-        <v>46242</v>
-      </c>
-      <c r="B17" s="9" t="str">
-        <f>TEXT(A17,"ddd")</f>
-        <v>Sat</v>
-      </c>
-      <c r="C17" s="10">
-        <v>33.619999999999997</v>
-      </c>
-      <c r="D17" s="11">
-        <v>1</v>
-      </c>
-      <c r="E17" s="10">
-        <f>C17*D17</f>
-        <v>33.619999999999997</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A18" s="14">
-        <v>46242</v>
-      </c>
-      <c r="B18" s="15" t="str">
+      <c r="B18" s="16" t="str">
         <f>TEXT(A18,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="17">
+        <v>7.6</v>
+      </c>
+      <c r="D18" s="18">
+        <v>1</v>
+      </c>
+      <c r="E18" s="17">
+        <f>C18*D18</f>
+        <v>7.6</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K18" s="13"/>
+      <c r="L18" s="19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A19" s="9">
+        <v>46242</v>
+      </c>
+      <c r="B19" s="10" t="str">
+        <f>TEXT(A19,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C19" s="11">
+        <v>33.619999999999997</v>
+      </c>
+      <c r="D19" s="12">
+        <v>1</v>
+      </c>
+      <c r="E19" s="11">
+        <f>C19*D19</f>
+        <v>33.619999999999997</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A20" s="15">
+        <v>46242</v>
+      </c>
+      <c r="B20" s="16" t="str">
+        <f>TEXT(A20,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C20" s="17">
         <v>4.96</v>
       </c>
-      <c r="D18" s="17">
-        <v>1</v>
-      </c>
-      <c r="E18" s="16">
-        <f>C18*D18</f>
+      <c r="D20" s="18">
+        <v>1</v>
+      </c>
+      <c r="E20" s="17">
+        <f>C20*D20</f>
         <v>4.96</v>
       </c>
-      <c r="F18" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I18" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" s="19" t="s">
+      <c r="F20" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20" s="19" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A19" s="8">
-        <v>46236</v>
-      </c>
-      <c r="B19" s="9" t="str">
-        <f>TEXT(A19,"ddd")</f>
-        <v>Sun</v>
-      </c>
-      <c r="C19" s="10">
-        <v>3.74</v>
-      </c>
-      <c r="D19" s="11">
-        <v>1</v>
-      </c>
-      <c r="E19" s="10">
-        <f>C19*D19</f>
-        <v>3.74</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A20" s="14">
+      <c r="J20" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" s="13"/>
+      <c r="L20" s="19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A21" s="9">
         <v>46243</v>
       </c>
-      <c r="B20" s="15" t="str">
-        <f>TEXT(A20,"ddd")</f>
-        <v>Sun</v>
-      </c>
-      <c r="C20" s="16">
-        <v>103.26</v>
-      </c>
-      <c r="D20" s="17">
-        <v>1</v>
-      </c>
-      <c r="E20" s="16">
-        <f>C20*D20</f>
-        <v>103.26</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H20" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A21" s="8">
-        <v>46243</v>
-      </c>
-      <c r="B21" s="9" t="str">
+      <c r="B21" s="10" t="str">
         <f>TEXT(A21,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="11">
         <v>113.65</v>
       </c>
-      <c r="D21" s="11">
-        <v>1</v>
-      </c>
-      <c r="E21" s="10">
+      <c r="D21" s="12">
+        <v>1</v>
+      </c>
+      <c r="E21" s="11">
         <f>C21*D21</f>
         <v>113.65</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I21" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" s="13" t="s">
+      <c r="F21" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I21" s="13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A22" s="14">
+      <c r="J21" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A22" s="15">
         <v>46243</v>
       </c>
-      <c r="B22" s="15" t="str">
+      <c r="B22" s="16" t="str">
         <f>TEXT(A22,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="17">
+        <v>103.26</v>
+      </c>
+      <c r="D22" s="18">
+        <v>1</v>
+      </c>
+      <c r="E22" s="17">
+        <f>C22*D22</f>
+        <v>103.26</v>
+      </c>
+      <c r="F22" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="17">
-        <v>1</v>
-      </c>
-      <c r="E22" s="16">
-        <f>C22*D22</f>
-        <v>16</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="I22" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="19" t="s">
+      <c r="G22" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" s="19" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A23" s="8">
-        <v>46236</v>
-      </c>
-      <c r="B23" s="9" t="str">
+      <c r="J22" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K22" s="13"/>
+      <c r="L22" s="19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A23" s="9">
+        <v>46243</v>
+      </c>
+      <c r="B23" s="10" t="str">
         <f>TEXT(A23,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C23" s="10">
-        <v>34.5</v>
-      </c>
-      <c r="D23" s="11">
-        <v>1</v>
-      </c>
-      <c r="E23" s="10">
+      <c r="C23" s="11">
+        <v>16</v>
+      </c>
+      <c r="D23" s="12">
+        <v>1</v>
+      </c>
+      <c r="E23" s="11">
         <f>C23*D23</f>
-        <v>34.5</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H23" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="I23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J23" s="13" t="s">
+      <c r="I23" s="13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A24" s="14"/>
-      <c r="B24" s="15" t="str">
+      <c r="J23" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A24" s="15"/>
+      <c r="B24" s="16" t="str">
         <f>IF(A24="","",TEXT(A24,"ddd"))</f>
         <v/>
       </c>
-      <c r="C24" s="20"/>
-      <c r="D24" s="17">
-        <v>1</v>
-      </c>
-      <c r="E24" s="16">
+      <c r="C24" s="21"/>
+      <c r="D24" s="18">
+        <v>1</v>
+      </c>
+      <c r="E24" s="17">
         <f>C24*D24</f>
         <v>0</v>
       </c>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="21"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9" t="str">
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="19"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A25" s="9"/>
+      <c r="B25" s="10" t="str">
         <f>IF(A25="","",TEXT(A25,"ddd"))</f>
         <v/>
       </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="11">
-        <v>1</v>
-      </c>
-      <c r="E25" s="10">
+      <c r="C25" s="23"/>
+      <c r="D25" s="12">
+        <v>1</v>
+      </c>
+      <c r="E25" s="11">
         <f>C25*D25</f>
         <v>0</v>
       </c>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="23"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A26" s="14"/>
-      <c r="B26" s="15" t="str">
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A26" s="15"/>
+      <c r="B26" s="16" t="str">
         <f>IF(A26="","",TEXT(A26,"ddd"))</f>
         <v/>
       </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="17">
-        <v>1</v>
-      </c>
-      <c r="E26" s="16">
+      <c r="C26" s="21"/>
+      <c r="D26" s="18">
+        <v>1</v>
+      </c>
+      <c r="E26" s="17">
         <f>C26*D26</f>
         <v>0</v>
       </c>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="21"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9" t="str">
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="19"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A27" s="9"/>
+      <c r="B27" s="10" t="str">
         <f>IF(A27="","",TEXT(A27,"ddd"))</f>
         <v/>
       </c>
-      <c r="C27" s="22"/>
-      <c r="D27" s="11">
-        <v>1</v>
-      </c>
-      <c r="E27" s="10">
+      <c r="C27" s="23"/>
+      <c r="D27" s="12">
+        <v>1</v>
+      </c>
+      <c r="E27" s="11">
         <f>C27*D27</f>
         <v>0</v>
       </c>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="23"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A28" s="14"/>
-      <c r="B28" s="15" t="str">
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="24"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A28" s="15"/>
+      <c r="B28" s="16" t="str">
         <f>IF(A28="","",TEXT(A28,"ddd"))</f>
         <v/>
       </c>
-      <c r="C28" s="20"/>
-      <c r="D28" s="17">
-        <v>1</v>
-      </c>
-      <c r="E28" s="16">
+      <c r="C28" s="21"/>
+      <c r="D28" s="18">
+        <v>1</v>
+      </c>
+      <c r="E28" s="17">
         <f>C28*D28</f>
         <v>0</v>
       </c>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="21"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9" t="str">
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="19"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A29" s="9"/>
+      <c r="B29" s="10" t="str">
         <f>IF(A29="","",TEXT(A29,"ddd"))</f>
         <v/>
       </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="11">
-        <v>1</v>
-      </c>
-      <c r="E29" s="10">
+      <c r="C29" s="23"/>
+      <c r="D29" s="12">
+        <v>1</v>
+      </c>
+      <c r="E29" s="11">
         <f>C29*D29</f>
         <v>0</v>
       </c>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="23"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A30" s="14"/>
-      <c r="B30" s="15" t="str">
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A30" s="15"/>
+      <c r="B30" s="16" t="str">
         <f>IF(A30="","",TEXT(A30,"ddd"))</f>
         <v/>
       </c>
-      <c r="C30" s="20"/>
-      <c r="D30" s="17">
-        <v>1</v>
-      </c>
-      <c r="E30" s="16">
+      <c r="C30" s="21"/>
+      <c r="D30" s="18">
+        <v>1</v>
+      </c>
+      <c r="E30" s="17">
         <f>C30*D30</f>
         <v>0</v>
       </c>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="21"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9" t="str">
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="19"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A31" s="9"/>
+      <c r="B31" s="10" t="str">
         <f>IF(A31="","",TEXT(A31,"ddd"))</f>
         <v/>
       </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="11">
-        <v>1</v>
-      </c>
-      <c r="E31" s="10">
+      <c r="C31" s="23"/>
+      <c r="D31" s="12">
+        <v>1</v>
+      </c>
+      <c r="E31" s="11">
         <f>C31*D31</f>
         <v>0</v>
       </c>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="23"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A32" s="14"/>
-      <c r="B32" s="15" t="str">
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A32" s="15"/>
+      <c r="B32" s="16" t="str">
         <f>IF(A32="","",TEXT(A32,"ddd"))</f>
         <v/>
       </c>
-      <c r="C32" s="20"/>
-      <c r="D32" s="17">
-        <v>1</v>
-      </c>
-      <c r="E32" s="16">
+      <c r="C32" s="21"/>
+      <c r="D32" s="18">
+        <v>1</v>
+      </c>
+      <c r="E32" s="17">
         <f>C32*D32</f>
         <v>0</v>
       </c>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="21"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9" t="str">
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="19"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A33" s="9"/>
+      <c r="B33" s="10" t="str">
         <f>IF(A33="","",TEXT(A33,"ddd"))</f>
         <v/>
       </c>
-      <c r="C33" s="22"/>
-      <c r="D33" s="11">
-        <v>1</v>
-      </c>
-      <c r="E33" s="10">
+      <c r="C33" s="23"/>
+      <c r="D33" s="12">
+        <v>1</v>
+      </c>
+      <c r="E33" s="11">
         <f>C33*D33</f>
         <v>0</v>
       </c>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="23"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A34" s="24"/>
-      <c r="B34" s="24"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="E34" s="26">
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A34" s="25"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" s="27">
         <f>SUM(E5:E33)</f>
-        <v>2463.56</v>
-      </c>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="24"/>
+        <v>2463.5600000000004</v>
+      </c>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F33" xr:uid="{E6D9AE04-0F43-46AA-863D-F00E64B85D66}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F33" xr:uid="{17B99C76-54A6-48D6-B9FB-132AC1406B11}">
       <formula1>"UF,PERSONAL,OTHER"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H33" xr:uid="{B0661D6E-323E-45D4-981F-EA9E6E27243F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H33" xr:uid="{BBED7A34-6F31-4F29-A43B-5EE0B31170A0}">
       <formula1>"Air Fare,Taxi/Train/Bus,Car Rental,Gas/Tolls,Parking,Hotel,Bkfst,Lunch,Dinner,Phone/Data,Computer,Other,Postage,Misc"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2224,7 +2387,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2318F84D-DF98-4C5B-B25F-41AB49DE6C53}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56389F32-CAE4-4001-8F12-3B12E6DC2BD4}">
   <sheetPr>
     <tabColor rgb="FFF0E4D6"/>
   </sheetPr>
@@ -2236,132 +2399,132 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/travel/trips/2026-08-02_2026-08-09_mohonk-expense-report.xlsx
+++ b/travel/trips/2026-08-02_2026-08-09_mohonk-expense-report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peter\Documents\Group-2\travel\trips\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F51C584-A73E-42D0-8761-0D9095DCD0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7EC3ABDD-310A-45DE-B94B-6C00EDDCFD16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2263" yWindow="2263" windowWidth="15428" windowHeight="9454" xr2:uid="{6A06982B-AC92-48BF-8175-DAEB804979ED}"/>
+    <workbookView xWindow="2263" yWindow="2263" windowWidth="15428" windowHeight="9454" xr2:uid="{130B8C68-8788-4F3A-B927-7780531E84BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -193,10 +193,10 @@
     <t>Other</t>
   </si>
   <si>
-    <t>Uber, Hotel Seville Nomad (3:01 AM) to EWR Terminal A (3:33 AM), UberX, driver Muhammad, 19.45 mi/31 min</t>
-  </si>
-  <si>
-    <t>Hotel Seville Nomad - mandatory fees, folio checkout ~4:17 AM (after physical departure via Uber) (Destination Fee /night x2 + NYC taxes), Hyatt folio 2529375976</t>
+    <t>Uber, Hotel Seville Nomad (3:01 AM) to EWR Terminal A (3:33 AM), UberX, driver Muhammad, 19.45 mi/31 min - fare+fees .65 + tip .04 (charged as 2 separate transactions 1 minute apart, combined here on one line)</t>
+  </si>
+  <si>
+    <t>Hotel Seville Nomad - mandatory fees, confirmed via property folio (Destination Fee /night x2 + NYC Sales Tax 8.875% + NYC Occupancy Tax 5.875%), Hyatt folio/confirmation 2529375976</t>
   </si>
   <si>
     <t>McDonald's #26777 (ORD Terminal 3, 6:56 AM) - breakfast, layover on return home</t>
@@ -271,7 +271,7 @@
     <t>-2674</t>
   </si>
   <si>
-    <t>Visa SW Rapid Rewards+ (flight cash balance, return flight, Taco Bell, gas, hotel + fees, both Ubers, Scarpetta, Chick Chick, E-ZPass, ORD breakfast, Budget rental car)</t>
+    <t>Visa SW Rapid Rewards+ (flight cash balance, return flight, Taco Bell, gas, hotel + fees, both Ubers + separate return tip, Scarpetta, Chick Chick, E-ZPass, ORD breakfast, Budget rental car)</t>
   </si>
   <si>
     <t>SW Credit</t>
@@ -922,7 +922,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{304F2538-6469-4F3D-933C-8B1D9CACBFBB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E75F4965-0C6F-47B7-8C7E-053EB55B29C1}">
   <sheetPr>
     <tabColor rgb="FF64381F"/>
   </sheetPr>
@@ -1090,7 +1090,7 @@
         <v>41</v>
       </c>
       <c r="B16" s="33">
-        <v>242.79</v>
+        <v>259.83</v>
       </c>
       <c r="C16" s="34">
         <v>2</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B23" s="27">
         <f>SUM(B13:B22)</f>
-        <v>2463.56</v>
+        <v>2480.6</v>
       </c>
       <c r="C23" s="25"/>
     </row>
@@ -1200,7 +1200,7 @@
         <v>76</v>
       </c>
       <c r="C27" s="11">
-        <v>2063.79</v>
+        <v>2080.83</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.4">
@@ -1254,7 +1254,7 @@
       <c r="B32" s="25"/>
       <c r="C32" s="27">
         <f>SUM(C27:C31)</f>
-        <v>2463.56</v>
+        <v>2480.6</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.4">
@@ -1316,7 +1316,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA6B548-1C31-4F3A-87A5-7F6E227AC84F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D64207-5B4D-42B3-9328-76414D9B2897}">
   <sheetPr>
     <tabColor rgb="FFB6752E"/>
   </sheetPr>
@@ -2026,14 +2026,14 @@
         <v>Sun</v>
       </c>
       <c r="C21" s="11">
-        <v>113.65</v>
+        <v>130.69</v>
       </c>
       <c r="D21" s="12">
         <v>1</v>
       </c>
       <c r="E21" s="11">
         <f>C21*D21</f>
-        <v>113.65</v>
+        <v>130.69</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>16</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="E34" s="27">
         <f>SUM(E5:E33)</f>
-        <v>2463.5600000000004</v>
+        <v>2480.6000000000004</v>
       </c>
       <c r="F34" s="25"/>
       <c r="G34" s="25"/>
@@ -2375,10 +2375,10 @@
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F33" xr:uid="{17B99C76-54A6-48D6-B9FB-132AC1406B11}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F33" xr:uid="{C2D18644-9A7C-49B6-988A-EF8C6E1D1EF6}">
       <formula1>"UF,PERSONAL,OTHER"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H33" xr:uid="{BBED7A34-6F31-4F29-A43B-5EE0B31170A0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H33" xr:uid="{4B445555-14E1-4BAD-9E77-5BDEC98C5494}">
       <formula1>"Air Fare,Taxi/Train/Bus,Car Rental,Gas/Tolls,Parking,Hotel,Bkfst,Lunch,Dinner,Phone/Data,Computer,Other,Postage,Misc"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2387,7 +2387,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56389F32-CAE4-4001-8F12-3B12E6DC2BD4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF7B1A7B-A31B-458D-9579-F0014AB1728D}">
   <sheetPr>
     <tabColor rgb="FFF0E4D6"/>
   </sheetPr>
